--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/13.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/13.xlsx
@@ -426,13 +426,13 @@
         <v>-15.14782382564544</v>
       </c>
       <c r="E2">
-        <v>-6.553949296158718</v>
+        <v>-4.430276125521628</v>
       </c>
       <c r="F2">
-        <v>-5.263578335052611</v>
+        <v>-5.29482766695582</v>
       </c>
       <c r="G2">
-        <v>-4.144519458919483</v>
+        <v>-3.674988095630189</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.40456882464342</v>
       </c>
       <c r="E3">
-        <v>-5.555792112336034</v>
+        <v>-4.497759445183932</v>
       </c>
       <c r="F3">
-        <v>-5.586820549503424</v>
+        <v>-5.115259979948763</v>
       </c>
       <c r="G3">
-        <v>-5.009968894886835</v>
+        <v>-3.794032002676842</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.96157327187385</v>
       </c>
       <c r="E4">
-        <v>-6.09836669709105</v>
+        <v>-5.647294458135021</v>
       </c>
       <c r="F4">
-        <v>-5.495617298455198</v>
+        <v>-5.280563180279612</v>
       </c>
       <c r="G4">
-        <v>-3.931489164012921</v>
+        <v>-3.599934717709373</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.58229264634451</v>
       </c>
       <c r="E5">
-        <v>-6.516000683974441</v>
+        <v>-6.213715987014429</v>
       </c>
       <c r="F5">
-        <v>-5.347584730105315</v>
+        <v>-5.079143161186704</v>
       </c>
       <c r="G5">
-        <v>-4.322981037304975</v>
+        <v>-3.554533896183807</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.21230814523286</v>
       </c>
       <c r="E6">
-        <v>-7.581885725055844</v>
+        <v>-7.452172115580134</v>
       </c>
       <c r="F6">
-        <v>-5.582998462306906</v>
+        <v>-4.677251603677093</v>
       </c>
       <c r="G6">
-        <v>-4.086194267608603</v>
+        <v>-3.929999418520249</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.71694760847664</v>
       </c>
       <c r="E7">
-        <v>-7.885628590646325</v>
+        <v>-7.886584098661944</v>
       </c>
       <c r="F7">
-        <v>-5.603396181233442</v>
+        <v>-5.137972985766122</v>
       </c>
       <c r="G7">
-        <v>-4.437006157314092</v>
+        <v>-3.99136369063618</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-23.99973748870146</v>
       </c>
       <c r="E8">
-        <v>-10.6441349469967</v>
+        <v>-8.049255941965479</v>
       </c>
       <c r="F8">
-        <v>-5.423057284174378</v>
+        <v>-5.252015154476934</v>
       </c>
       <c r="G8">
-        <v>-4.703942065236607</v>
+        <v>-4.085134893036036</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-24.94568106343551</v>
       </c>
       <c r="E9">
-        <v>-10.54914567621181</v>
+        <v>-8.656777900938502</v>
       </c>
       <c r="F9">
-        <v>-5.350332424780401</v>
+        <v>-4.837445433867476</v>
       </c>
       <c r="G9">
-        <v>-4.346184650989726</v>
+        <v>-3.448341526920605</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-25.47824015432616</v>
       </c>
       <c r="E10">
-        <v>-10.13488087399012</v>
+        <v>-9.21426022212677</v>
       </c>
       <c r="F10">
-        <v>-5.195244651260874</v>
+        <v>-4.996885449721311</v>
       </c>
       <c r="G10">
-        <v>-4.230414873481413</v>
+        <v>-3.645206427958906</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-25.53642817575859</v>
       </c>
       <c r="E11">
-        <v>-11.35091652774385</v>
+        <v>-10.41570060415378</v>
       </c>
       <c r="F11">
-        <v>-5.325806951085716</v>
+        <v>-4.681865610110687</v>
       </c>
       <c r="G11">
-        <v>-3.304094436683481</v>
+        <v>-3.751918552871774</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-25.10329836708092</v>
       </c>
       <c r="E12">
-        <v>-11.78584022838853</v>
+        <v>-11.40970064883742</v>
       </c>
       <c r="F12">
-        <v>-5.155690107777199</v>
+        <v>-4.657609355821911</v>
       </c>
       <c r="G12">
-        <v>-3.0622657061308</v>
+        <v>-3.061156673375144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-24.18746353522857</v>
       </c>
       <c r="E13">
-        <v>-12.03592520546212</v>
+        <v>-11.83693500061707</v>
       </c>
       <c r="F13">
-        <v>-4.847606188430214</v>
+        <v>-4.486300491820765</v>
       </c>
       <c r="G13">
-        <v>-3.447100072343379</v>
+        <v>-2.725450802965349</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-22.84075164242244</v>
       </c>
       <c r="E14">
-        <v>-12.99932182280193</v>
+        <v>-12.49185649702838</v>
       </c>
       <c r="F14">
-        <v>-4.503062506216414</v>
+        <v>-4.289501934468076</v>
       </c>
       <c r="G14">
-        <v>-2.495881022544589</v>
+        <v>-2.052986308664272</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-21.13983630762025</v>
       </c>
       <c r="E15">
-        <v>-13.8345852680947</v>
+        <v>-12.95750136534109</v>
       </c>
       <c r="F15">
-        <v>-4.564826408136548</v>
+        <v>-4.229155369174132</v>
       </c>
       <c r="G15">
-        <v>-2.684221268819266</v>
+        <v>-1.463460911758555</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.18189933851888</v>
       </c>
       <c r="E16">
-        <v>-13.88103382599138</v>
+        <v>-13.92104742232316</v>
       </c>
       <c r="F16">
-        <v>-4.264324535627387</v>
+        <v>-4.071140145253112</v>
       </c>
       <c r="G16">
-        <v>-2.59530994727106</v>
+        <v>-1.269731097345944</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.07974823423057</v>
       </c>
       <c r="E17">
-        <v>-15.57789832140554</v>
+        <v>-14.6995600313518</v>
       </c>
       <c r="F17">
-        <v>-4.264027151729782</v>
+        <v>-3.860603942892395</v>
       </c>
       <c r="G17">
-        <v>-1.552365612215683</v>
+        <v>-0.4886277406281433</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.95208686449231</v>
       </c>
       <c r="E18">
-        <v>-15.65638130443248</v>
+        <v>-16.31526068712649</v>
       </c>
       <c r="F18">
-        <v>-3.824733977616371</v>
+        <v>-3.224577652451115</v>
       </c>
       <c r="G18">
-        <v>-1.279642870690522</v>
+        <v>-0.1276888921180236</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.92228563826656</v>
       </c>
       <c r="E19">
-        <v>-17.27306011059282</v>
+        <v>-16.18426551950661</v>
       </c>
       <c r="F19">
-        <v>-3.588263248608807</v>
+        <v>-2.991902502883179</v>
       </c>
       <c r="G19">
-        <v>-0.3558715539578294</v>
+        <v>-0.2373242287420675</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.09794609600184</v>
       </c>
       <c r="E20">
-        <v>-17.96025151278278</v>
+        <v>-17.47082762745579</v>
       </c>
       <c r="F20">
-        <v>-3.474062033356659</v>
+        <v>-2.817786301753945</v>
       </c>
       <c r="G20">
-        <v>-0.3793466323768014</v>
+        <v>-0.450218791281519</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.567625762016149</v>
       </c>
       <c r="E21">
-        <v>-18.78336506231298</v>
+        <v>-18.55951353516582</v>
       </c>
       <c r="F21">
-        <v>-3.169468854245073</v>
+        <v>-2.579368909349803</v>
       </c>
       <c r="G21">
-        <v>-1.364704027776556</v>
+        <v>0.2358553557315025</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.388826280921386</v>
       </c>
       <c r="E22">
-        <v>-19.62504082680061</v>
+        <v>-18.19282035239471</v>
       </c>
       <c r="F22">
-        <v>-2.918209281995329</v>
+        <v>-2.477063050001855</v>
       </c>
       <c r="G22">
-        <v>-0.652181932450297</v>
+        <v>-0.003834762402809948</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.597221733204093</v>
       </c>
       <c r="E23">
-        <v>-19.28816311689601</v>
+        <v>-18.66318841909742</v>
       </c>
       <c r="F23">
-        <v>-2.65140125359504</v>
+        <v>-2.168305667956396</v>
       </c>
       <c r="G23">
-        <v>-0.5859478478460984</v>
+        <v>-0.1148009383336409</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.197155107946302</v>
       </c>
       <c r="E24">
-        <v>-19.68553671106908</v>
+        <v>-19.69389627408724</v>
       </c>
       <c r="F24">
-        <v>-2.307198030383789</v>
+        <v>-1.704571513623385</v>
       </c>
       <c r="G24">
-        <v>-0.9864609577326658</v>
+        <v>0.150102294627761</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.162001724219467</v>
       </c>
       <c r="E25">
-        <v>-20.57432671913252</v>
+        <v>-19.86684322491418</v>
       </c>
       <c r="F25">
-        <v>-2.117578104943759</v>
+        <v>-1.7819236333294</v>
       </c>
       <c r="G25">
-        <v>-1.02318814994534</v>
+        <v>-0.5378555527971058</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.447323150784282</v>
       </c>
       <c r="E26">
-        <v>-20.90336111205584</v>
+        <v>-19.85366536555186</v>
       </c>
       <c r="F26">
-        <v>-1.803929213384769</v>
+        <v>-1.822434112795907</v>
       </c>
       <c r="G26">
-        <v>-1.667320995521335</v>
+        <v>-1.093265777920633</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.98796362100589</v>
       </c>
       <c r="E27">
-        <v>-20.6281566896617</v>
+        <v>-19.59652502597432</v>
       </c>
       <c r="F27">
-        <v>-2.079708460757377</v>
+        <v>-1.540035381507527</v>
       </c>
       <c r="G27">
-        <v>-1.431696227309248</v>
+        <v>-0.7919697178460229</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.716921729101086</v>
       </c>
       <c r="E28">
-        <v>-22.01306819610947</v>
+        <v>-20.07215970794795</v>
       </c>
       <c r="F28">
-        <v>-1.937877879152254</v>
+        <v>-1.492198820730662</v>
       </c>
       <c r="G28">
-        <v>-2.633622890797045</v>
+        <v>-1.500303973065104</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.561331515199383</v>
       </c>
       <c r="E29">
-        <v>-21.49247029571368</v>
+        <v>-19.69868739958736</v>
       </c>
       <c r="F29">
-        <v>-1.775206402060099</v>
+        <v>-1.42670146692611</v>
       </c>
       <c r="G29">
-        <v>-1.981329550466747</v>
+        <v>-1.227534883902394</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.45480193852566</v>
       </c>
       <c r="E30">
-        <v>-21.14065767853178</v>
+        <v>-19.55154822213013</v>
       </c>
       <c r="F30">
-        <v>-2.02384667658219</v>
+        <v>-1.419781285643123</v>
       </c>
       <c r="G30">
-        <v>-2.128605789872304</v>
+        <v>-2.165637552274592</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.34560667862011</v>
       </c>
       <c r="E31">
-        <v>-21.28609867823613</v>
+        <v>-19.46937453278695</v>
       </c>
       <c r="F31">
-        <v>-1.68273574888559</v>
+        <v>-1.641612277541011</v>
       </c>
       <c r="G31">
-        <v>-2.519458727875278</v>
+        <v>-1.344774543630143</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.1968015116068</v>
       </c>
       <c r="E32">
-        <v>-20.05438997594185</v>
+        <v>-19.69817568202449</v>
       </c>
       <c r="F32">
-        <v>-1.903163486403135</v>
+        <v>-1.754393671064761</v>
       </c>
       <c r="G32">
-        <v>-2.677812052655237</v>
+        <v>-1.575330866621607</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.98718463750864</v>
       </c>
       <c r="E33">
-        <v>-20.34707883647961</v>
+        <v>-19.2434625499663</v>
       </c>
       <c r="F33">
-        <v>-2.016084874017959</v>
+        <v>-1.741886980017294</v>
       </c>
       <c r="G33">
-        <v>-1.997971662892663</v>
+        <v>-1.957288368760559</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.70530858187859</v>
       </c>
       <c r="E34">
-        <v>-19.61369247093739</v>
+        <v>-19.30469657549801</v>
       </c>
       <c r="F34">
-        <v>-2.100044880496105</v>
+        <v>-1.814505808383713</v>
       </c>
       <c r="G34">
-        <v>-2.35464983929374</v>
+        <v>-1.150521663022328</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.3544779521921</v>
       </c>
       <c r="E35">
-        <v>-19.85468427220358</v>
+        <v>-18.2279431967982</v>
       </c>
       <c r="F35">
-        <v>-2.046898484667294</v>
+        <v>-1.845389830262287</v>
       </c>
       <c r="G35">
-        <v>-2.42151623809594</v>
+        <v>-1.787924169516985</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.93983355359263</v>
       </c>
       <c r="E36">
-        <v>-17.99949074005925</v>
+        <v>-18.37715188687693</v>
       </c>
       <c r="F36">
-        <v>-2.25620041959784</v>
+        <v>-2.103490888891751</v>
       </c>
       <c r="G36">
-        <v>-1.647643112835907</v>
+        <v>-1.534180785568466</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.46872509932548</v>
       </c>
       <c r="E37">
-        <v>-19.52966663572507</v>
+        <v>-17.38686971935359</v>
       </c>
       <c r="F37">
-        <v>-2.372267118241093</v>
+        <v>-1.927675706219376</v>
       </c>
       <c r="G37">
-        <v>-2.592078854824731</v>
+        <v>-1.162499216783411</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.94204823914797</v>
       </c>
       <c r="E38">
-        <v>-18.62272197536488</v>
+        <v>-16.81239203521453</v>
       </c>
       <c r="F38">
-        <v>-2.678160834175074</v>
+        <v>-2.179159766035278</v>
       </c>
       <c r="G38">
-        <v>-1.591264522302119</v>
+        <v>-0.9910460633045565</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.35274208992611</v>
       </c>
       <c r="E39">
-        <v>-17.37502323134952</v>
+        <v>-16.56384673930355</v>
       </c>
       <c r="F39">
-        <v>-2.170065120319942</v>
+        <v>-2.037947146512643</v>
       </c>
       <c r="G39">
-        <v>-2.189883987804214</v>
+        <v>-0.4164545373264922</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-16.69203836270253</v>
       </c>
       <c r="E40">
-        <v>-17.33332504268689</v>
+        <v>-16.1381520686865</v>
       </c>
       <c r="F40">
-        <v>-2.209729008300788</v>
+        <v>-2.194815081580785</v>
       </c>
       <c r="G40">
-        <v>-0.7254045786878971</v>
+        <v>-0.7463835057702587</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-16.94191815217051</v>
       </c>
       <c r="E41">
-        <v>-17.39054231177381</v>
+        <v>-16.06563761440168</v>
       </c>
       <c r="F41">
-        <v>-2.318407498078471</v>
+        <v>-2.084430154953334</v>
       </c>
       <c r="G41">
-        <v>-1.742923924001671</v>
+        <v>-0.3264176302949337</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.0845350146053</v>
       </c>
       <c r="E42">
-        <v>-17.38190651184118</v>
+        <v>-14.28887725207019</v>
       </c>
       <c r="F42">
-        <v>-2.407695563691425</v>
+        <v>-2.204524375908998</v>
       </c>
       <c r="G42">
-        <v>-0.8319114497773298</v>
+        <v>-0.1323071031453069</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.10082550785963</v>
       </c>
       <c r="E43">
-        <v>-15.26542908640228</v>
+        <v>-15.37136367886371</v>
       </c>
       <c r="F43">
-        <v>-2.481803796648077</v>
+        <v>-2.479106632384562</v>
       </c>
       <c r="G43">
-        <v>-1.207850380125887</v>
+        <v>-0.1765889602785983</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-16.97709608859422</v>
       </c>
       <c r="E44">
-        <v>-15.4190032254244</v>
+        <v>-13.97539363888921</v>
       </c>
       <c r="F44">
-        <v>-2.724580886693153</v>
+        <v>-2.456918811500577</v>
       </c>
       <c r="G44">
-        <v>-0.4287201085494919</v>
+        <v>-0.3016017809325569</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-16.70282938103734</v>
       </c>
       <c r="E45">
-        <v>-14.7646794875821</v>
+        <v>-14.25482765600651</v>
       </c>
       <c r="F45">
-        <v>-2.986758341311794</v>
+        <v>-2.542629986668242</v>
       </c>
       <c r="G45">
-        <v>-0.9028398879562149</v>
+        <v>-0.05293346329574092</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.28105296206119</v>
       </c>
       <c r="E46">
-        <v>-15.25752237078489</v>
+        <v>-13.67237532913995</v>
       </c>
       <c r="F46">
-        <v>-3.124308748546652</v>
+        <v>-2.762965775404077</v>
       </c>
       <c r="G46">
-        <v>-0.1662534371049937</v>
+        <v>0.8075402227260867</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.72539163967185</v>
       </c>
       <c r="E47">
-        <v>-14.76357906839824</v>
+        <v>-13.36954268682501</v>
       </c>
       <c r="F47">
-        <v>-2.853321606599239</v>
+        <v>-2.565502867394342</v>
       </c>
       <c r="G47">
-        <v>-0.6811756902832341</v>
+        <v>0.4654880365175091</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.05831883888288</v>
       </c>
       <c r="E48">
-        <v>-13.50807323519366</v>
+        <v>-12.51075381906239</v>
       </c>
       <c r="F48">
-        <v>-3.093012199701484</v>
+        <v>-2.7689499015219</v>
       </c>
       <c r="G48">
-        <v>-0.520693684721524</v>
+        <v>0.306787104455927</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.3154656388956</v>
       </c>
       <c r="E49">
-        <v>-12.1382823034575</v>
+        <v>-12.92835610662773</v>
       </c>
       <c r="F49">
-        <v>-3.111218886847614</v>
+        <v>-2.678879857080704</v>
       </c>
       <c r="G49">
-        <v>-1.353292577302688</v>
+        <v>0.7992473061502124</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.53578348686566</v>
       </c>
       <c r="E50">
-        <v>-11.83662706438455</v>
+        <v>-11.75812596746159</v>
       </c>
       <c r="F50">
-        <v>-3.072012257673113</v>
+        <v>-3.141697008698817</v>
       </c>
       <c r="G50">
-        <v>-0.5081301643999899</v>
+        <v>0.4623330866185837</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.7682542376032</v>
       </c>
       <c r="E51">
-        <v>-12.03597501867621</v>
+        <v>-10.80355534596273</v>
       </c>
       <c r="F51">
-        <v>-2.949725348202239</v>
+        <v>-3.18668647071226</v>
       </c>
       <c r="G51">
-        <v>-1.074365873436934</v>
+        <v>0.5702138341068139</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.05982598179442</v>
       </c>
       <c r="E52">
-        <v>-11.75772746174891</v>
+        <v>-11.09608570991022</v>
       </c>
       <c r="F52">
-        <v>-3.206390846122652</v>
+        <v>-2.86352460789952</v>
       </c>
       <c r="G52">
-        <v>-0.5986868270812139</v>
+        <v>0.881729548261154</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.45486523485369</v>
       </c>
       <c r="E53">
-        <v>-11.30038781476627</v>
+        <v>-10.44826033226893</v>
       </c>
       <c r="F53">
-        <v>-3.517485880978812</v>
+        <v>-3.188450893280223</v>
       </c>
       <c r="G53">
-        <v>-0.4749419453687962</v>
+        <v>0.7922090863337219</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.99037996009561</v>
       </c>
       <c r="E54">
-        <v>-10.46856148124531</v>
+        <v>-9.499228034481449</v>
       </c>
       <c r="F54">
-        <v>-3.536229350201956</v>
+        <v>-2.818716558347289</v>
       </c>
       <c r="G54">
-        <v>-0.8484509352915286</v>
+        <v>0.9130075825161882</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.69494948974061</v>
       </c>
       <c r="E55">
-        <v>-11.83882790275228</v>
+        <v>-8.965782853325898</v>
       </c>
       <c r="F55">
-        <v>-3.447930355267946</v>
+        <v>-3.273129094296597</v>
       </c>
       <c r="G55">
-        <v>-0.957030207888545</v>
+        <v>0.06678248449538374</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.58556887328729</v>
       </c>
       <c r="E56">
-        <v>-10.25298800458417</v>
+        <v>-8.988081059339667</v>
       </c>
       <c r="F56">
-        <v>-3.200761261253227</v>
+        <v>-3.325836455401924</v>
       </c>
       <c r="G56">
-        <v>-0.839409835423779</v>
+        <v>0.5549489086252345</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.66062912253992</v>
       </c>
       <c r="E57">
-        <v>-10.6995136556365</v>
+        <v>-8.799017269519428</v>
       </c>
       <c r="F57">
-        <v>-3.589611002373162</v>
+        <v>-3.566231160796549</v>
       </c>
       <c r="G57">
-        <v>-1.304266708411621</v>
+        <v>0.8255098639132508</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.90833247549927</v>
       </c>
       <c r="E58">
-        <v>-10.50895094091972</v>
+        <v>-8.584163820225509</v>
       </c>
       <c r="F58">
-        <v>-3.202835493229837</v>
+        <v>-3.700892222530442</v>
       </c>
       <c r="G58">
-        <v>-1.063017323328312</v>
+        <v>0.4865331745106561</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.300794976852</v>
       </c>
       <c r="E59">
-        <v>-9.050614756911585</v>
+        <v>-8.49202295959144</v>
       </c>
       <c r="F59">
-        <v>-3.690946015125029</v>
+        <v>-3.413833924601315</v>
       </c>
       <c r="G59">
-        <v>-1.339083715848136</v>
+        <v>0.7440373381917869</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.80894443757042</v>
       </c>
       <c r="E60">
-        <v>-9.156218770770458</v>
+        <v>-8.11423501550154</v>
       </c>
       <c r="F60">
-        <v>-3.645640116763715</v>
+        <v>-3.360656050811198</v>
       </c>
       <c r="G60">
-        <v>-0.8396548157936851</v>
+        <v>0.8276915134236305</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.39792657980235</v>
       </c>
       <c r="E61">
-        <v>-8.744698223797423</v>
+        <v>-7.58585719676057</v>
       </c>
       <c r="F61">
-        <v>-3.841793375909624</v>
+        <v>-3.314809228535857</v>
       </c>
       <c r="G61">
-        <v>-1.608462806378633</v>
+        <v>0.3279348693607914</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.03138770658066</v>
       </c>
       <c r="E62">
-        <v>-8.513184518629282</v>
+        <v>-7.286484308587491</v>
       </c>
       <c r="F62">
-        <v>-3.605498260791454</v>
+        <v>-3.287443283016973</v>
       </c>
       <c r="G62">
-        <v>-1.956066777456568</v>
+        <v>0.469808298446258</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.67950930931995</v>
       </c>
       <c r="E63">
-        <v>-8.547025804888603</v>
+        <v>-6.449341546581533</v>
       </c>
       <c r="F63">
-        <v>-3.535536006685813</v>
+        <v>-3.47165065584711</v>
       </c>
       <c r="G63">
-        <v>-2.035509938762459</v>
+        <v>0.1958109968884783</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.31205016547584</v>
       </c>
       <c r="E64">
-        <v>-7.839492497456179</v>
+        <v>-6.422840916688647</v>
       </c>
       <c r="F64">
-        <v>-3.632810362429157</v>
+        <v>-3.531459610696637</v>
       </c>
       <c r="G64">
-        <v>-1.162807097518563</v>
+        <v>0.0002537613381899677</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.9040405646111</v>
       </c>
       <c r="E65">
-        <v>-7.526334934403751</v>
+        <v>-6.979508112555533</v>
       </c>
       <c r="F65">
-        <v>-3.853726008346951</v>
+        <v>-3.819463075832358</v>
       </c>
       <c r="G65">
-        <v>-2.220456875859383</v>
+        <v>-0.1219020585153776</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.43164102863054</v>
       </c>
       <c r="E66">
-        <v>-8.194216923425014</v>
+        <v>-6.120737358688942</v>
       </c>
       <c r="F66">
-        <v>-3.876294878236223</v>
+        <v>-3.339997396152782</v>
       </c>
       <c r="G66">
-        <v>-1.623542341310013</v>
+        <v>-0.6467559483114316</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.88133594842842</v>
       </c>
       <c r="E67">
-        <v>-7.145834434383257</v>
+        <v>-6.293652610197826</v>
       </c>
       <c r="F67">
-        <v>-4.101624065676134</v>
+        <v>-3.58721950568128</v>
       </c>
       <c r="G67">
-        <v>-1.893153170028259</v>
+        <v>0.0254006652544939</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.24471772246751</v>
       </c>
       <c r="E68">
-        <v>-7.613739011225797</v>
+        <v>-6.372452586405299</v>
       </c>
       <c r="F68">
-        <v>-3.744227434840496</v>
+        <v>-3.638831765080106</v>
       </c>
       <c r="G68">
-        <v>-1.469171602813798</v>
+        <v>-0.02420785965148483</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.52238313558888</v>
       </c>
       <c r="E69">
-        <v>-7.138579819022969</v>
+        <v>-5.681013475596134</v>
       </c>
       <c r="F69">
-        <v>-4.02435229760819</v>
+        <v>-3.616923104010865</v>
       </c>
       <c r="G69">
-        <v>-2.203669099429739</v>
+        <v>-0.2069565945103329</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-16.71993775503783</v>
       </c>
       <c r="E70">
-        <v>-7.393487620914734</v>
+        <v>-5.561045142184931</v>
       </c>
       <c r="F70">
-        <v>-3.736692604944631</v>
+        <v>-3.609915944150583</v>
       </c>
       <c r="G70">
-        <v>-2.012918776002472</v>
+        <v>-0.4579820205711099</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-16.84426687815107</v>
       </c>
       <c r="E71">
-        <v>-7.746296502378324</v>
+        <v>-6.268592035039378</v>
       </c>
       <c r="F71">
-        <v>-3.837186824782656</v>
+        <v>-3.839429215342034</v>
       </c>
       <c r="G71">
-        <v>-2.056233953838297</v>
+        <v>-0.1041608449704233</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-16.91229283647259</v>
       </c>
       <c r="E72">
-        <v>-6.829846575076035</v>
+        <v>-5.330364676234203</v>
       </c>
       <c r="F72">
-        <v>-3.724298571863945</v>
+        <v>-3.781871763093316</v>
       </c>
       <c r="G72">
-        <v>-1.948740540178161</v>
+        <v>-0.1183498431517396</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-16.93608860784724</v>
       </c>
       <c r="E73">
-        <v>-7.082779962300455</v>
+        <v>-5.418882757662136</v>
       </c>
       <c r="F73">
-        <v>-4.048760971499081</v>
+        <v>-3.825324603574567</v>
       </c>
       <c r="G73">
-        <v>-1.304101181134658</v>
+        <v>-0.03516245484093319</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-16.93087853341919</v>
       </c>
       <c r="E74">
-        <v>-6.904779234480957</v>
+        <v>-6.177864058295703</v>
       </c>
       <c r="F74">
-        <v>-4.374528878161028</v>
+        <v>-3.841826510605736</v>
       </c>
       <c r="G74">
-        <v>-1.786371523659066</v>
+        <v>0.4354713201129373</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-16.90628309245034</v>
       </c>
       <c r="E75">
-        <v>-7.655006994857697</v>
+        <v>-6.165714162533123</v>
       </c>
       <c r="F75">
-        <v>-4.090718608818278</v>
+        <v>-3.97892877107568</v>
       </c>
       <c r="G75">
-        <v>-0.3437516467385576</v>
+        <v>0.6702750730312855</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-16.87034130696189</v>
       </c>
       <c r="E76">
-        <v>-7.571855155128854</v>
+        <v>-6.813598410336514</v>
       </c>
       <c r="F76">
-        <v>-4.320181349598158</v>
+        <v>-4.153170055682736</v>
       </c>
       <c r="G76">
-        <v>-1.10018481809771</v>
+        <v>1.180168607535373</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-16.82803351032768</v>
       </c>
       <c r="E77">
-        <v>-8.129563900017505</v>
+        <v>-7.570003009259716</v>
       </c>
       <c r="F77">
-        <v>-4.422579986095219</v>
+        <v>-4.123981701877693</v>
       </c>
       <c r="G77">
-        <v>-0.9150657326327435</v>
+        <v>1.382125127613073</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.78322458926578</v>
       </c>
       <c r="E78">
-        <v>-8.62877381767507</v>
+        <v>-7.578829005100666</v>
       </c>
       <c r="F78">
-        <v>-4.256579300411212</v>
+        <v>-4.252319835226017</v>
       </c>
       <c r="G78">
-        <v>-1.405880593194011</v>
+        <v>0.9410876297802865</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.73860571432427</v>
       </c>
       <c r="E79">
-        <v>-10.74843476034136</v>
+        <v>-7.711223471188917</v>
       </c>
       <c r="F79">
-        <v>-4.637445236502966</v>
+        <v>-4.406965260552449</v>
       </c>
       <c r="G79">
-        <v>-0.2135710644977967</v>
+        <v>1.597075538932411</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.69300846406519</v>
       </c>
       <c r="E80">
-        <v>-9.048015412831184</v>
+        <v>-7.978951382996396</v>
       </c>
       <c r="F80">
-        <v>-4.565490758793593</v>
+        <v>-4.42761645990424</v>
       </c>
       <c r="G80">
-        <v>-0.8557440671145431</v>
+        <v>0.9185990939320172</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.65287278045221</v>
       </c>
       <c r="E81">
-        <v>-9.322400181429938</v>
+        <v>-9.00473225826587</v>
       </c>
       <c r="F81">
-        <v>-4.522635999577163</v>
+        <v>-4.247361227952859</v>
       </c>
       <c r="G81">
-        <v>-0.05703853976443719</v>
+        <v>1.072863894970976</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.62104132184004</v>
       </c>
       <c r="E82">
-        <v>-11.30272450735422</v>
+        <v>-10.14563599975834</v>
       </c>
       <c r="F82">
-        <v>-5.128021808156292</v>
+        <v>-4.816137339165264</v>
       </c>
       <c r="G82">
-        <v>-0.05841903725431328</v>
+        <v>1.555693719691521</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.60657140600164</v>
       </c>
       <c r="E83">
-        <v>-12.42676874011614</v>
+        <v>-10.31152758808133</v>
       </c>
       <c r="F83">
-        <v>-4.744490185762329</v>
+        <v>-4.831168065689061</v>
       </c>
       <c r="G83">
-        <v>-0.1691501644518559</v>
+        <v>2.320082131981542</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.61217527610775</v>
       </c>
       <c r="E84">
-        <v>-12.83513294070583</v>
+        <v>-11.74890599438197</v>
       </c>
       <c r="F84">
-        <v>-5.062390258832488</v>
+        <v>-4.895652326159989</v>
       </c>
       <c r="G84">
-        <v>-0.4182058159167666</v>
+        <v>1.989368564244969</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.63524075761948</v>
       </c>
       <c r="E85">
-        <v>-14.38891577137363</v>
+        <v>-12.85251322394727</v>
       </c>
       <c r="F85">
-        <v>-5.173705442053282</v>
+        <v>-5.25758592526076</v>
       </c>
       <c r="G85">
-        <v>-0.2026164693083484</v>
+        <v>2.065415105827567</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.67280299817306</v>
       </c>
       <c r="E86">
-        <v>-15.19622494661706</v>
+        <v>-13.54795550577921</v>
       </c>
       <c r="F86">
-        <v>-5.314666237885466</v>
+        <v>-5.502192050531217</v>
       </c>
       <c r="G86">
-        <v>-0.2438724878187459</v>
+        <v>1.665967991604645</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.71765845555679</v>
       </c>
       <c r="E87">
-        <v>-16.26838645267309</v>
+        <v>-15.42340037368585</v>
       </c>
       <c r="F87">
-        <v>-5.307567129243473</v>
+        <v>-5.301685720683597</v>
       </c>
       <c r="G87">
-        <v>-0.4820794815514649</v>
+        <v>2.597396600169672</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.7648239941041</v>
       </c>
       <c r="E88">
-        <v>-17.98740877140678</v>
+        <v>-16.46671550031302</v>
       </c>
       <c r="F88">
-        <v>-5.469446687098553</v>
+        <v>-5.618790561047067</v>
       </c>
       <c r="G88">
-        <v>0.4042760494963849</v>
+        <v>2.680875316487934</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.80641724447685</v>
       </c>
       <c r="E89">
-        <v>-19.56110330228632</v>
+        <v>-17.92311802591989</v>
       </c>
       <c r="F89">
-        <v>-5.846955250106761</v>
+        <v>-5.806651034123551</v>
       </c>
       <c r="G89">
-        <v>-0.9350051484157739</v>
+        <v>1.769799941898346</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.8420436676369</v>
       </c>
       <c r="E90">
-        <v>-20.31650710845382</v>
+        <v>-19.18169869297568</v>
       </c>
       <c r="F90">
-        <v>-5.729647657094114</v>
+        <v>-6.069226933462938</v>
       </c>
       <c r="G90">
-        <v>-0.6029806046456486</v>
+        <v>1.990970868285976</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.8704194351417</v>
       </c>
       <c r="E91">
-        <v>-22.62774061554061</v>
+        <v>-21.6406691360887</v>
       </c>
       <c r="F91">
-        <v>-6.053164061155253</v>
+        <v>-6.146225340287957</v>
       </c>
       <c r="G91">
-        <v>-0.3515612236656984</v>
+        <v>2.194887231322924</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.90064945893871</v>
       </c>
       <c r="E92">
-        <v>-23.71626802666036</v>
+        <v>-24.12110454599808</v>
       </c>
       <c r="F92">
-        <v>-5.860186762631677</v>
+        <v>-6.142052853680056</v>
       </c>
       <c r="G92">
-        <v>-0.6925474142106306</v>
+        <v>1.480954843596935</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.94302047643973</v>
       </c>
       <c r="E93">
-        <v>-26.15335235489431</v>
+        <v>-26.30639666245754</v>
       </c>
       <c r="F93">
-        <v>-6.22296115464629</v>
+        <v>-6.26584283580331</v>
       </c>
       <c r="G93">
-        <v>-1.559933519318456</v>
+        <v>1.570660696074567</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.0059361892012</v>
       </c>
       <c r="E94">
-        <v>-28.97516224939791</v>
+        <v>-27.60570189626431</v>
       </c>
       <c r="F94">
-        <v>-6.261078894869811</v>
+        <v>-6.29681425044288</v>
       </c>
       <c r="G94">
-        <v>-1.458279907989595</v>
+        <v>1.310796113423935</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.10393963542726</v>
       </c>
       <c r="E95">
-        <v>-30.5956495021987</v>
+        <v>-30.43645552693306</v>
       </c>
       <c r="F95">
-        <v>-5.840752434994598</v>
+        <v>-6.399105199177576</v>
       </c>
       <c r="G95">
-        <v>-2.187530189925792</v>
+        <v>0.9242303318943176</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.24276897276026</v>
       </c>
       <c r="E96">
-        <v>-32.42374464588114</v>
+        <v>-32.52741500133874</v>
       </c>
       <c r="F96">
-        <v>-6.567993573627743</v>
+        <v>-6.699998475284559</v>
       </c>
       <c r="G96">
-        <v>-2.137958081020745</v>
+        <v>0.3784637259266875</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.42199982604165</v>
       </c>
       <c r="E97">
-        <v>-35.49931210987855</v>
+        <v>-35.00590090318781</v>
       </c>
       <c r="F97">
-        <v>-6.379348636620809</v>
+        <v>-7.206407218923891</v>
       </c>
       <c r="G97">
-        <v>-2.300446277179253</v>
+        <v>0.08049476411904499</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.6361945040495</v>
       </c>
       <c r="E98">
-        <v>-38.31838454184452</v>
+        <v>-37.27669060891209</v>
       </c>
       <c r="F98">
-        <v>-6.196190805290018</v>
+        <v>-7.103673921996099</v>
       </c>
       <c r="G98">
-        <v>-3.703280017808801</v>
+        <v>-0.3686568808304947</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.86758246131487</v>
       </c>
       <c r="E99">
-        <v>-41.38612453851967</v>
+        <v>-39.64203258767952</v>
       </c>
       <c r="F99">
-        <v>-6.98831547748224</v>
+        <v>-7.141782135994488</v>
       </c>
       <c r="G99">
-        <v>-3.041359611050302</v>
+        <v>-0.9686667754590832</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.11292145801416</v>
       </c>
       <c r="E100">
-        <v>-42.55130316493026</v>
+        <v>-41.97974861076316</v>
       </c>
       <c r="F100">
-        <v>-6.504193130447826</v>
+        <v>-7.330975866405776</v>
       </c>
       <c r="G100">
-        <v>-3.587109664290236</v>
+        <v>-1.718561619378175</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.34649620066913</v>
       </c>
       <c r="E101">
-        <v>-45.57272819369197</v>
+        <v>-46.22711759440737</v>
       </c>
       <c r="F101">
-        <v>-6.501651699256037</v>
+        <v>-7.312216658201979</v>
       </c>
       <c r="G101">
-        <v>-3.608542136111478</v>
+        <v>-1.886406278219224</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.58732120976735</v>
       </c>
       <c r="E102">
-        <v>-48.63441701697437</v>
+        <v>-48.28395728140227</v>
       </c>
       <c r="F102">
-        <v>-6.658201955425206</v>
+        <v>-7.499856371365616</v>
       </c>
       <c r="G102">
-        <v>-4.383636852675501</v>
+        <v>-2.531072121627041</v>
       </c>
     </row>
   </sheetData>
